--- a/results/benchmark_new_algorithm.xlsx
+++ b/results/benchmark_new_algorithm.xlsx
@@ -1,106 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29924"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8607d062d2dc3d62/EV-projects/evcs-projects/results/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_2B59D2BFD34051513120CAF0504160B2641BF433" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB9CED0A-95F7-4658-BD1F-B5536C695B3D}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>Instance</t>
-  </si>
-  <si>
-    <t>Policy</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>seed</t>
-  </si>
-  <si>
-    <t>Exact_aligned</t>
-  </si>
-  <si>
-    <t>Exact_incumbent_raw</t>
-  </si>
-  <si>
-    <t>Exact_bound_raw</t>
-  </si>
-  <si>
-    <t>Exact_gap_raw</t>
-  </si>
-  <si>
-    <t>DR_aligned</t>
-  </si>
-  <si>
-    <t>DR_iters</t>
-  </si>
-  <si>
-    <t>Gap_aligned</t>
-  </si>
-  <si>
-    <t>Gap_aligned_%</t>
-  </si>
-  <si>
-    <t>Gap_raw_inc</t>
-  </si>
-  <si>
-    <t>Gap_raw_inc_%</t>
-  </si>
-  <si>
-    <t>DR_time</t>
-  </si>
-  <si>
-    <t>Exact_time</t>
-  </si>
-  <si>
-    <t>Total_time</t>
-  </si>
-  <si>
-    <t>center_58_Trieste_k225</t>
-  </si>
-  <si>
-    <t>closest_priority</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -119,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -421,129 +408,253 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Instance</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Exact_aligned</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Exact_incumbent_raw</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Exact_bound_raw</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Exact_gap_raw</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>DR_aligned</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>DR_iters</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Gap_aligned</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Gap_aligned_%</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Gap_raw_inc</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Gap_raw_inc_%</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>DR_time</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Exact_time</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Total_time</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>center_58_Trieste_k225</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>closest_priority</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>225</v>
+      </c>
+      <c r="D2" t="n">
+        <v>225</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" t="n">
+        <v>490.9943618774414</v>
+      </c>
+      <c r="H2" t="n">
+        <v>491.0003618774414</v>
+      </c>
+      <c r="I2" t="n">
+        <v>491.0003618774414</v>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="K2" t="n">
+        <v>490.9943618774414</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.005999999999971806</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.001221995026038182</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>336.8575358390808</v>
+      </c>
+      <c r="R2" t="n">
+        <v>17.60576033592224</v>
+      </c>
+      <c r="S2" t="n">
+        <v>373.1175796985626</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>center_102_Vicenza_k125</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>closest_priority</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>125</v>
+      </c>
+      <c r="D3" t="n">
+        <v>125</v>
+      </c>
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="F3" t="n">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="G3" t="n">
+        <v>298.6922922808684</v>
+      </c>
+      <c r="H3" t="n">
+        <v>298.8864695175763</v>
+      </c>
+      <c r="I3" t="n">
+        <v>298.8864695175764</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.803679634782884e-16</v>
+      </c>
+      <c r="K3" t="n">
+        <v>285.0069887678671</v>
+      </c>
+      <c r="L3" t="n">
+        <v>406</v>
+      </c>
+      <c r="M3" t="n">
+        <v>13.68530351300126</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.581739759167471</v>
+      </c>
+      <c r="O3" t="n">
+        <v>13.87948074970916</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.643730033049543</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>184.9753177165985</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.6534144878387451</v>
+      </c>
+      <c r="S3" t="n">
+        <v>185.7377293109894</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U3" t="n">
         <v>20</v>
-      </c>
-      <c r="C2">
-        <v>225</v>
-      </c>
-      <c r="D2">
-        <v>225</v>
-      </c>
-      <c r="E2">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>490.99436187744141</v>
-      </c>
-      <c r="H2">
-        <v>491.00036187744138</v>
-      </c>
-      <c r="I2">
-        <v>491.00036187744138</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>490.99436187744141</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>5.9999999999718057E-3</v>
-      </c>
-      <c r="P2">
-        <v>1.2219950260381821E-3</v>
-      </c>
-      <c r="Q2">
-        <v>336.85753583908081</v>
-      </c>
-      <c r="R2">
-        <v>17.605760335922241</v>
-      </c>
-      <c r="S2">
-        <v>373.11757969856262</v>
       </c>
     </row>
   </sheetData>

--- a/results/benchmark_new_algorithm.xlsx
+++ b/results/benchmark_new_algorithm.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,6 +657,75 @@
         <v>20</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>center_146_Verona_k250</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>closest_priority</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>250</v>
+      </c>
+      <c r="D4" t="n">
+        <v>250</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" t="n">
+        <v>402.4877814673246</v>
+      </c>
+      <c r="H4" t="n">
+        <v>402.725041529487</v>
+      </c>
+      <c r="I4" t="n">
+        <v>402.9892231891375</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0006559851819672517</v>
+      </c>
+      <c r="K4" t="n">
+        <v>372.11103616721</v>
+      </c>
+      <c r="L4" t="n">
+        <v>420</v>
+      </c>
+      <c r="M4" t="n">
+        <v>30.37674530011458</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7.547246574634383</v>
+      </c>
+      <c r="O4" t="n">
+        <v>30.614005362277</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7.601713875553844</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>384.957483291626</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.6268115043640137</v>
+      </c>
+      <c r="S4" t="n">
+        <v>385.7850403785706</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
